--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/117.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/117.xlsx
@@ -426,13 +426,13 @@
         <v>-18.38488711541069</v>
       </c>
       <c r="E2">
-        <v>-28.75546733491585</v>
+        <v>-19.75724012167075</v>
       </c>
       <c r="F2">
-        <v>-4.621348401131766</v>
+        <v>-2.196545541085233</v>
       </c>
       <c r="G2">
-        <v>-19.02607348637876</v>
+        <v>-16.08559185340787</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.18771243332399</v>
       </c>
       <c r="E3">
-        <v>-29.88454690604976</v>
+        <v>-19.47331828908282</v>
       </c>
       <c r="F3">
-        <v>-4.92110888481542</v>
+        <v>-1.938249816116111</v>
       </c>
       <c r="G3">
-        <v>-18.24217001007879</v>
+        <v>-15.6583369742107</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.95268985550258</v>
       </c>
       <c r="E4">
-        <v>-29.48577216748503</v>
+        <v>-20.86096018445526</v>
       </c>
       <c r="F4">
-        <v>-4.913067922436445</v>
+        <v>-2.027675390717929</v>
       </c>
       <c r="G4">
-        <v>-17.17311317730365</v>
+        <v>-15.53358254392435</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.68909644862463</v>
       </c>
       <c r="E5">
-        <v>-29.9980998568819</v>
+        <v>-20.81010411178274</v>
       </c>
       <c r="F5">
-        <v>-4.707039695481764</v>
+        <v>-2.026073328160915</v>
       </c>
       <c r="G5">
-        <v>-18.01993298750486</v>
+        <v>-15.29250638838095</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.40232872025931</v>
       </c>
       <c r="E6">
-        <v>-31.93544419036335</v>
+        <v>-21.39569029573826</v>
       </c>
       <c r="F6">
-        <v>-4.610038700981344</v>
+        <v>-2.046186088700887</v>
       </c>
       <c r="G6">
-        <v>-17.66420989935961</v>
+        <v>-14.93427959617282</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.11686686947127</v>
       </c>
       <c r="E7">
-        <v>-30.26709920117972</v>
+        <v>-22.14458905540869</v>
       </c>
       <c r="F7">
-        <v>-4.288475587256007</v>
+        <v>-1.587839635955684</v>
       </c>
       <c r="G7">
-        <v>-18.08773402453607</v>
+        <v>-14.64646458558701</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.83266007166001</v>
       </c>
       <c r="E8">
-        <v>-32.3592960189074</v>
+        <v>-22.24922506152642</v>
       </c>
       <c r="F8">
-        <v>-4.640817520199763</v>
+        <v>-1.328709745011943</v>
       </c>
       <c r="G8">
-        <v>-17.25675229639685</v>
+        <v>-14.03266939461021</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.58077147591486</v>
       </c>
       <c r="E9">
-        <v>-32.38487980066834</v>
+        <v>-23.01638549139213</v>
       </c>
       <c r="F9">
-        <v>-4.097090410880612</v>
+        <v>-1.697086385771688</v>
       </c>
       <c r="G9">
-        <v>-17.85208169088071</v>
+        <v>-13.90436043556306</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.36253736236283</v>
       </c>
       <c r="E10">
-        <v>-33.26016908737596</v>
+        <v>-23.85302084029956</v>
       </c>
       <c r="F10">
-        <v>-4.412474732148468</v>
+        <v>-1.539944261093219</v>
       </c>
       <c r="G10">
-        <v>-16.69709219988908</v>
+        <v>-13.79746219290763</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.19122659991762</v>
       </c>
       <c r="E11">
-        <v>-31.92349747798748</v>
+        <v>-25.40382579577922</v>
       </c>
       <c r="F11">
-        <v>-3.98762828553988</v>
+        <v>-1.334803215626936</v>
       </c>
       <c r="G11">
-        <v>-16.40665600173379</v>
+        <v>-13.21928669575968</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-16.07819075718297</v>
       </c>
       <c r="E12">
-        <v>-32.86015669183642</v>
+        <v>-25.36353549271706</v>
       </c>
       <c r="F12">
-        <v>-4.22449166069637</v>
+        <v>-1.177035673559353</v>
       </c>
       <c r="G12">
-        <v>-17.19505387484737</v>
+        <v>-12.98583913591151</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-16.0087666953313</v>
       </c>
       <c r="E13">
-        <v>-32.57871224980375</v>
+        <v>-26.12241857241238</v>
       </c>
       <c r="F13">
-        <v>-3.885573421514981</v>
+        <v>-0.9082047719614269</v>
       </c>
       <c r="G13">
-        <v>-16.11153873852664</v>
+        <v>-12.65718033157004</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.98649585209942</v>
       </c>
       <c r="E14">
-        <v>-34.44956574658035</v>
+        <v>-26.54183892447284</v>
       </c>
       <c r="F14">
-        <v>-3.858286999266765</v>
+        <v>-0.8730380906103795</v>
       </c>
       <c r="G14">
-        <v>-16.01580012362593</v>
+        <v>-12.55271660824582</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.97801287675772</v>
       </c>
       <c r="E15">
-        <v>-37.18969468006622</v>
+        <v>-27.33838747767303</v>
       </c>
       <c r="F15">
-        <v>-3.257558272226175</v>
+        <v>-0.5249448540755824</v>
       </c>
       <c r="G15">
-        <v>-16.57706191194035</v>
+        <v>-12.65134792815349</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.96016780056125</v>
       </c>
       <c r="E16">
-        <v>-35.85453068638865</v>
+        <v>-28.17661350651787</v>
       </c>
       <c r="F16">
-        <v>-2.674076982879273</v>
+        <v>-0.07269601378238677</v>
       </c>
       <c r="G16">
-        <v>-15.53878967401132</v>
+        <v>-11.85158026234562</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-15.9066003384122</v>
       </c>
       <c r="E17">
-        <v>-36.68526016879218</v>
+        <v>-29.06638711772083</v>
       </c>
       <c r="F17">
-        <v>-3.191257402040908</v>
+        <v>-0.1534179320829902</v>
       </c>
       <c r="G17">
-        <v>-16.69459502268768</v>
+        <v>-11.68865021927572</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-15.78101195247965</v>
       </c>
       <c r="E18">
-        <v>-36.93888017155416</v>
+        <v>-29.66057667893573</v>
       </c>
       <c r="F18">
-        <v>-3.062791700112552</v>
+        <v>0.02493951014857696</v>
       </c>
       <c r="G18">
-        <v>-15.3505706534596</v>
+        <v>-11.70596859352087</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-15.5788408452961</v>
       </c>
       <c r="E19">
-        <v>-38.42849378797946</v>
+        <v>-30.41788569153895</v>
       </c>
       <c r="F19">
-        <v>-3.333083841809017</v>
+        <v>0.3287101204291837</v>
       </c>
       <c r="G19">
-        <v>-15.29052483323629</v>
+        <v>-11.57421867310263</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-15.28113888718912</v>
       </c>
       <c r="E20">
-        <v>-39.00553058642282</v>
+        <v>-31.34519810330136</v>
       </c>
       <c r="F20">
-        <v>-1.918398819675424</v>
+        <v>0.7191793198215922</v>
       </c>
       <c r="G20">
-        <v>-15.2914934194796</v>
+        <v>-11.08190403869492</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-14.89479373604417</v>
       </c>
       <c r="E21">
-        <v>-39.2215640266951</v>
+        <v>-31.70333782226398</v>
       </c>
       <c r="F21">
-        <v>-1.659982981432896</v>
+        <v>0.8277451516324954</v>
       </c>
       <c r="G21">
-        <v>-15.0130757840495</v>
+        <v>-11.18892107022924</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-14.43027556304591</v>
       </c>
       <c r="E22">
-        <v>-38.68032168005477</v>
+        <v>-32.51311435353374</v>
       </c>
       <c r="F22">
-        <v>-2.091149042957441</v>
+        <v>1.13825867257189</v>
       </c>
       <c r="G22">
-        <v>-14.99640748520754</v>
+        <v>-10.99856646060199</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-13.89761936083195</v>
       </c>
       <c r="E23">
-        <v>-39.96591501996485</v>
+        <v>-32.45036763683824</v>
       </c>
       <c r="F23">
-        <v>-2.173526039328838</v>
+        <v>0.9292599201107693</v>
       </c>
       <c r="G23">
-        <v>-14.86432208410934</v>
+        <v>-11.19370525969246</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-13.33365323652901</v>
       </c>
       <c r="E24">
-        <v>-39.54591529492458</v>
+        <v>-32.43539531001223</v>
       </c>
       <c r="F24">
-        <v>-2.090714150070971</v>
+        <v>1.14576865144567</v>
       </c>
       <c r="G24">
-        <v>-14.31355026756202</v>
+        <v>-11.14620406722945</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-12.75765309291183</v>
       </c>
       <c r="E25">
-        <v>-41.69111539557971</v>
+        <v>-32.74473064269679</v>
       </c>
       <c r="F25">
-        <v>-2.019158117082345</v>
+        <v>1.513881871371326</v>
       </c>
       <c r="G25">
-        <v>-14.90482778644047</v>
+        <v>-10.97967250199611</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-12.21420624662756</v>
       </c>
       <c r="E26">
-        <v>-40.70924017003736</v>
+        <v>-32.84674181925723</v>
       </c>
       <c r="F26">
-        <v>-1.9019101665227</v>
+        <v>1.192853054620794</v>
       </c>
       <c r="G26">
-        <v>-15.28307637891785</v>
+        <v>-10.47323765546736</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.73642411776744</v>
       </c>
       <c r="E27">
-        <v>-40.32581154731786</v>
+        <v>-32.66346268009821</v>
       </c>
       <c r="F27">
-        <v>-2.250840882501727</v>
+        <v>1.228141505980053</v>
       </c>
       <c r="G27">
-        <v>-15.22108033248498</v>
+        <v>-11.26346827128389</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.34619535616067</v>
       </c>
       <c r="E28">
-        <v>-40.89517321123294</v>
+        <v>-32.44908844775019</v>
       </c>
       <c r="F28">
-        <v>-2.137416675873405</v>
+        <v>0.995643627036316</v>
       </c>
       <c r="G28">
-        <v>-14.41552203517402</v>
+        <v>-10.84137613951565</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.0724073091297</v>
       </c>
       <c r="E29">
-        <v>-39.38412902437154</v>
+        <v>-32.5188686278243</v>
       </c>
       <c r="F29">
-        <v>-2.252612760376315</v>
+        <v>1.023032766842479</v>
       </c>
       <c r="G29">
-        <v>-14.12203387659172</v>
+        <v>-11.11118353928426</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.91165925688065</v>
       </c>
       <c r="E30">
-        <v>-39.20288288215603</v>
+        <v>-32.79057586590591</v>
       </c>
       <c r="F30">
-        <v>-2.121781241145564</v>
+        <v>0.9737366227018803</v>
       </c>
       <c r="G30">
-        <v>-15.22664643995323</v>
+        <v>-11.13644118783098</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.87628647849001</v>
       </c>
       <c r="E31">
-        <v>-39.42034295051838</v>
+        <v>-32.72053195691267</v>
       </c>
       <c r="F31">
-        <v>-2.359600552284885</v>
+        <v>0.9733820814534822</v>
       </c>
       <c r="G31">
-        <v>-14.22687224176476</v>
+        <v>-11.21794210710406</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.95473140382662</v>
       </c>
       <c r="E32">
-        <v>-39.08356319739936</v>
+        <v>-32.36115665758092</v>
       </c>
       <c r="F32">
-        <v>-2.303539959933026</v>
+        <v>1.149590738642187</v>
       </c>
       <c r="G32">
-        <v>-14.8618967023842</v>
+        <v>-11.07022356739428</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.13206758169952</v>
       </c>
       <c r="E33">
-        <v>-39.05021083385532</v>
+        <v>-31.69716199702396</v>
       </c>
       <c r="F33">
-        <v>-2.083119677722105</v>
+        <v>1.084022145240995</v>
       </c>
       <c r="G33">
-        <v>-15.14914126527685</v>
+        <v>-10.89457528204877</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.39873584401686</v>
       </c>
       <c r="E34">
-        <v>-39.51045310002753</v>
+        <v>-31.60724704844708</v>
       </c>
       <c r="F34">
-        <v>-1.420591428963061</v>
+        <v>1.075982011229423</v>
       </c>
       <c r="G34">
-        <v>-15.08506837152175</v>
+        <v>-10.96223925498895</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.72167916415756</v>
       </c>
       <c r="E35">
-        <v>-37.90688990108858</v>
+        <v>-31.14670990427082</v>
       </c>
       <c r="F35">
-        <v>-2.923626804809638</v>
+        <v>1.20415198599498</v>
       </c>
       <c r="G35">
-        <v>-15.48087552674666</v>
+        <v>-10.9243560455996</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-12.09153367856774</v>
       </c>
       <c r="E36">
-        <v>-37.54920495876603</v>
+        <v>-30.13029657335119</v>
       </c>
       <c r="F36">
-        <v>-2.161049169507872</v>
+        <v>1.021326329992712</v>
       </c>
       <c r="G36">
-        <v>-14.2382877224894</v>
+        <v>-11.14771177223082</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-12.48098316144906</v>
       </c>
       <c r="E37">
-        <v>-38.82628629206587</v>
+        <v>-29.98878005066899</v>
       </c>
       <c r="F37">
-        <v>-1.767629325426691</v>
+        <v>1.069273892001553</v>
       </c>
       <c r="G37">
-        <v>-15.11667012942488</v>
+        <v>-11.51069011959477</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-12.87638976832216</v>
       </c>
       <c r="E38">
-        <v>-36.90907465048153</v>
+        <v>-30.52935373028602</v>
       </c>
       <c r="F38">
-        <v>-1.877825384286304</v>
+        <v>1.034552043945809</v>
       </c>
       <c r="G38">
-        <v>-15.60191225673526</v>
+        <v>-11.29791704616363</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-13.27227987189725</v>
       </c>
       <c r="E39">
-        <v>-37.00060519826376</v>
+        <v>-29.3262784695833</v>
       </c>
       <c r="F39">
-        <v>-2.07820911575831</v>
+        <v>0.7578027783445219</v>
       </c>
       <c r="G39">
-        <v>-15.42901830693338</v>
+        <v>-10.95343582422771</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-13.65247492905034</v>
       </c>
       <c r="E40">
-        <v>-35.20820794001884</v>
+        <v>-29.70462563824687</v>
       </c>
       <c r="F40">
-        <v>-2.017693563514195</v>
+        <v>0.9742369566131712</v>
       </c>
       <c r="G40">
-        <v>-15.61975016915404</v>
+        <v>-11.80744170891596</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-14.02768914553831</v>
       </c>
       <c r="E41">
-        <v>-36.05165040228766</v>
+        <v>-28.65060705538658</v>
       </c>
       <c r="F41">
-        <v>-2.201244040993912</v>
+        <v>0.9591871776391098</v>
       </c>
       <c r="G41">
-        <v>-15.94450982644869</v>
+        <v>-11.52973811213154</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-14.38888768890614</v>
       </c>
       <c r="E42">
-        <v>-36.00410859225235</v>
+        <v>-27.99886436823786</v>
       </c>
       <c r="F42">
-        <v>-1.837719976479766</v>
+        <v>1.295196190501868</v>
       </c>
       <c r="G42">
-        <v>-15.00625521380522</v>
+        <v>-11.39670892686365</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-14.74210516993894</v>
       </c>
       <c r="E43">
-        <v>-35.63932788838134</v>
+        <v>-27.40620941860748</v>
       </c>
       <c r="F43">
-        <v>-1.928279586056016</v>
+        <v>1.054346711403106</v>
       </c>
       <c r="G43">
-        <v>-16.92171935913617</v>
+        <v>-11.38189686742597</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-15.09023574893745</v>
       </c>
       <c r="E44">
-        <v>-35.49503909713981</v>
+        <v>-27.64003936940665</v>
       </c>
       <c r="F44">
-        <v>-1.755039797638945</v>
+        <v>1.120001455014189</v>
       </c>
       <c r="G44">
-        <v>-16.19464657109555</v>
+        <v>-11.63713239625928</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-15.4226760452337</v>
       </c>
       <c r="E45">
-        <v>-34.85322881487441</v>
+        <v>-27.21238735250038</v>
       </c>
       <c r="F45">
-        <v>-2.39281642840234</v>
+        <v>0.7973026495796136</v>
       </c>
       <c r="G45">
-        <v>-16.08179583077239</v>
+        <v>-11.30543337984145</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-15.74946344735652</v>
       </c>
       <c r="E46">
-        <v>-35.57306963151068</v>
+        <v>-26.54626209453378</v>
       </c>
       <c r="F46">
-        <v>-1.360708749414685</v>
+        <v>1.033152103035078</v>
       </c>
       <c r="G46">
-        <v>-15.71253081043303</v>
+        <v>-11.06287562674259</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-16.05392695564693</v>
       </c>
       <c r="E47">
-        <v>-33.68685132943788</v>
+        <v>-27.06196219152642</v>
       </c>
       <c r="F47">
-        <v>-2.126244484711848</v>
+        <v>1.051967640222266</v>
       </c>
       <c r="G47">
-        <v>-16.68665183226922</v>
+        <v>-11.49738184904157</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-16.33773014678554</v>
       </c>
       <c r="E48">
-        <v>-33.17457140197124</v>
+        <v>-25.53822371425067</v>
       </c>
       <c r="F48">
-        <v>-1.731209324195208</v>
+        <v>1.144903835877148</v>
       </c>
       <c r="G48">
-        <v>-14.92636512394486</v>
+        <v>-11.40473305036444</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-16.59787667183357</v>
       </c>
       <c r="E49">
-        <v>-31.7551553633582</v>
+        <v>-25.15846653034232</v>
       </c>
       <c r="F49">
-        <v>-2.041937392291928</v>
+        <v>1.074696385020278</v>
       </c>
       <c r="G49">
-        <v>-15.79670513216741</v>
+        <v>-11.37580077880572</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-16.82382315777767</v>
       </c>
       <c r="E50">
-        <v>-33.01555739997753</v>
+        <v>-25.58386750671054</v>
       </c>
       <c r="F50">
-        <v>-2.207199174252638</v>
+        <v>0.7952830898515884</v>
       </c>
       <c r="G50">
-        <v>-15.3833576894071</v>
+        <v>-11.48452915341952</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-17.02959394275024</v>
       </c>
       <c r="E51">
-        <v>-32.22854877319047</v>
+        <v>-24.44599558720196</v>
       </c>
       <c r="F51">
-        <v>-2.581772831552727</v>
+        <v>0.9161286400415914</v>
       </c>
       <c r="G51">
-        <v>-16.41093370674633</v>
+        <v>-11.19438666403074</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-17.204806468443</v>
       </c>
       <c r="E52">
-        <v>-32.52763605693101</v>
+        <v>-24.28918278721041</v>
       </c>
       <c r="F52">
-        <v>-2.329298044323077</v>
+        <v>0.8388552152388424</v>
       </c>
       <c r="G52">
-        <v>-16.14216146720811</v>
+        <v>-11.41996674505359</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-17.36360864798123</v>
       </c>
       <c r="E53">
-        <v>-32.5521566165928</v>
+        <v>-23.69554767970737</v>
       </c>
       <c r="F53">
-        <v>-2.255603166700422</v>
+        <v>0.8492760771660601</v>
       </c>
       <c r="G53">
-        <v>-15.83463664033169</v>
+        <v>-11.65961482330565</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-17.50838240316109</v>
       </c>
       <c r="E54">
-        <v>-31.92625728691283</v>
+        <v>-23.56785719752551</v>
       </c>
       <c r="F54">
-        <v>-2.666969590563253</v>
+        <v>0.4804877378071231</v>
       </c>
       <c r="G54">
-        <v>-15.24861585568745</v>
+        <v>-11.66654373945046</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-17.6310374759379</v>
       </c>
       <c r="E55">
-        <v>-30.96331862840603</v>
+        <v>-24.04024345361151</v>
       </c>
       <c r="F55">
-        <v>-1.879236093973272</v>
+        <v>0.86172146902572</v>
       </c>
       <c r="G55">
-        <v>-15.55013466463201</v>
+        <v>-11.69590939461131</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-17.7413133934594</v>
       </c>
       <c r="E56">
-        <v>-29.21531919922352</v>
+        <v>-22.69039578129501</v>
       </c>
       <c r="F56">
-        <v>-2.053876651668478</v>
+        <v>0.5950451510424751</v>
       </c>
       <c r="G56">
-        <v>-16.22910317820907</v>
+        <v>-11.55063842795569</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-17.82037280110654</v>
       </c>
       <c r="E57">
-        <v>-30.57165003441807</v>
+        <v>-22.48452940234591</v>
       </c>
       <c r="F57">
-        <v>-2.279040993995231</v>
+        <v>0.7833893906821932</v>
       </c>
       <c r="G57">
-        <v>-16.31639995047442</v>
+        <v>-11.60500587869333</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-17.87556638435097</v>
       </c>
       <c r="E58">
-        <v>-30.55409648675369</v>
+        <v>-22.56496879928519</v>
       </c>
       <c r="F58">
-        <v>-2.324183703978193</v>
+        <v>0.7248089046910177</v>
       </c>
       <c r="G58">
-        <v>-16.12407683942547</v>
+        <v>-12.10223001830463</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-17.90058634602959</v>
       </c>
       <c r="E59">
-        <v>-29.94225162419693</v>
+        <v>-21.79156609279827</v>
       </c>
       <c r="F59">
-        <v>-2.261586464450843</v>
+        <v>0.6960421898939992</v>
       </c>
       <c r="G59">
-        <v>-16.28618971943835</v>
+        <v>-12.03809707742393</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-17.88784944307733</v>
       </c>
       <c r="E60">
-        <v>-29.03264019910093</v>
+        <v>-20.9986017609714</v>
       </c>
       <c r="F60">
-        <v>-2.30531349454242</v>
+        <v>0.5941223497557565</v>
       </c>
       <c r="G60">
-        <v>-16.38086706666278</v>
+        <v>-12.21914046646698</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-17.84942231017717</v>
       </c>
       <c r="E61">
-        <v>-29.64826240735762</v>
+        <v>-21.94223214002907</v>
       </c>
       <c r="F61">
-        <v>-2.156656337170826</v>
+        <v>0.6646263561428279</v>
       </c>
       <c r="G61">
-        <v>-17.23797059980838</v>
+        <v>-11.97677068697868</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-17.77214311315007</v>
       </c>
       <c r="E62">
-        <v>-29.83758654559993</v>
+        <v>-20.46404608456405</v>
       </c>
       <c r="F62">
-        <v>-2.288177886448109</v>
+        <v>0.7437901153587655</v>
       </c>
       <c r="G62">
-        <v>-15.77994154114787</v>
+        <v>-12.50713170231269</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-17.67086979370123</v>
       </c>
       <c r="E63">
-        <v>-30.29119198007505</v>
+        <v>-21.52801991496995</v>
       </c>
       <c r="F63">
-        <v>-2.449895912659643</v>
+        <v>0.8353893260255293</v>
       </c>
       <c r="G63">
-        <v>-16.31903158102226</v>
+        <v>-12.69889480864684</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-17.54288654179406</v>
       </c>
       <c r="E64">
-        <v>-30.46455117398472</v>
+        <v>-20.96779323936383</v>
       </c>
       <c r="F64">
-        <v>-2.046085856245148</v>
+        <v>0.7695937599559701</v>
       </c>
       <c r="G64">
-        <v>-16.663242590893</v>
+        <v>-12.5478762877739</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-17.38437332334436</v>
       </c>
       <c r="E65">
-        <v>-29.57026925188866</v>
+        <v>-20.17377399186046</v>
       </c>
       <c r="F65">
-        <v>-2.066816578867609</v>
+        <v>0.3895603331040298</v>
       </c>
       <c r="G65">
-        <v>-16.85150860484736</v>
+        <v>-12.67519185850413</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-17.20418616914144</v>
       </c>
       <c r="E66">
-        <v>-28.87815112084562</v>
+        <v>-20.4996847909424</v>
       </c>
       <c r="F66">
-        <v>-2.275029210663473</v>
+        <v>0.4460889530384708</v>
       </c>
       <c r="G66">
-        <v>-16.7655955272153</v>
+        <v>-12.96317004062688</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-16.98688087861679</v>
       </c>
       <c r="E67">
-        <v>-26.82127113561863</v>
+        <v>-20.05384586164471</v>
       </c>
       <c r="F67">
-        <v>-2.146184944832038</v>
+        <v>0.6197636343420123</v>
       </c>
       <c r="G67">
-        <v>-16.60669255767719</v>
+        <v>-12.98914433856386</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-16.74554018124613</v>
       </c>
       <c r="E68">
-        <v>-30.03372610362628</v>
+        <v>-21.06928526450866</v>
       </c>
       <c r="F68">
-        <v>-2.408974562961347</v>
+        <v>0.5363089319795734</v>
       </c>
       <c r="G68">
-        <v>-16.87906109788968</v>
+        <v>-12.83548896565389</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-16.47683121459388</v>
       </c>
       <c r="E69">
-        <v>-28.70600881785413</v>
+        <v>-20.57994144658339</v>
       </c>
       <c r="F69">
-        <v>-3.242110876898769</v>
+        <v>0.4405529736855617</v>
       </c>
       <c r="G69">
-        <v>-16.46392137896757</v>
+        <v>-12.97941800958967</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-16.18462950294348</v>
       </c>
       <c r="E70">
-        <v>-27.71163657943537</v>
+        <v>-21.37617850893422</v>
       </c>
       <c r="F70">
-        <v>-2.831790681065674</v>
+        <v>0.4481863793023592</v>
       </c>
       <c r="G70">
-        <v>-16.24782613304424</v>
+        <v>-13.04410181757909</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-15.88544657307688</v>
       </c>
       <c r="E71">
-        <v>-28.64905790756242</v>
+        <v>-20.46508438739525</v>
       </c>
       <c r="F71">
-        <v>-2.43484282021597</v>
+        <v>0.2297434100819211</v>
       </c>
       <c r="G71">
-        <v>-17.09497620243622</v>
+        <v>-12.38698523622965</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-15.57452711276558</v>
       </c>
       <c r="E72">
-        <v>-29.44729681777181</v>
+        <v>-20.66255297304555</v>
       </c>
       <c r="F72">
-        <v>-3.109763445320895</v>
+        <v>0.4302315158466799</v>
       </c>
       <c r="G72">
-        <v>-16.35043883845335</v>
+        <v>-12.68083237219323</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-15.27436237562151</v>
       </c>
       <c r="E73">
-        <v>-28.63156042825092</v>
+        <v>-20.40620846365449</v>
       </c>
       <c r="F73">
-        <v>-2.892205172486647</v>
+        <v>0.4550311791516915</v>
       </c>
       <c r="G73">
-        <v>-16.38427930984336</v>
+        <v>-12.56701565637135</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-14.98509281125101</v>
       </c>
       <c r="E74">
-        <v>-29.64887708263369</v>
+        <v>-21.56347172683869</v>
       </c>
       <c r="F74">
-        <v>-2.648116776842939</v>
+        <v>0.4711578357493922</v>
       </c>
       <c r="G74">
-        <v>-15.49457540898853</v>
+        <v>-12.52944704170523</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-14.71401573325721</v>
       </c>
       <c r="E75">
-        <v>-29.0340066056268</v>
+        <v>-21.0436142653099</v>
       </c>
       <c r="F75">
-        <v>-3.419457710898921</v>
+        <v>0.2368491456631353</v>
       </c>
       <c r="G75">
-        <v>-16.2074118067738</v>
+        <v>-12.24023006127399</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-14.4733352328986</v>
       </c>
       <c r="E76">
-        <v>-28.85959249604063</v>
+        <v>-21.16499601948934</v>
       </c>
       <c r="F76">
-        <v>-2.931917934144258</v>
+        <v>0.1618678134639324</v>
       </c>
       <c r="G76">
-        <v>-16.47127454110844</v>
+        <v>-12.22799872286463</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-14.25369503447744</v>
       </c>
       <c r="E77">
-        <v>-29.11141415829896</v>
+        <v>-21.49147580852278</v>
       </c>
       <c r="F77">
-        <v>-2.78056361250915</v>
+        <v>-0.05560679426263297</v>
       </c>
       <c r="G77">
-        <v>-16.96024742243953</v>
+        <v>-13.13404588485983</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-14.06958132644793</v>
       </c>
       <c r="E78">
-        <v>-28.77045212137583</v>
+        <v>-21.41481998710042</v>
       </c>
       <c r="F78">
-        <v>-2.986685444980348</v>
+        <v>0.3720751539657378</v>
       </c>
       <c r="G78">
-        <v>-16.43040072378997</v>
+        <v>-12.65696102902438</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-13.90899281768769</v>
       </c>
       <c r="E79">
-        <v>-29.37138857438793</v>
+        <v>-21.81760257459362</v>
       </c>
       <c r="F79">
-        <v>-2.694962610206057</v>
+        <v>-0.08674346819906079</v>
       </c>
       <c r="G79">
-        <v>-16.76945681846556</v>
+        <v>-12.31371991076924</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-13.77033784852276</v>
       </c>
       <c r="E80">
-        <v>-28.32330493051082</v>
+        <v>-22.03094888713873</v>
       </c>
       <c r="F80">
-        <v>-2.649397432847667</v>
+        <v>0.03681664196991628</v>
       </c>
       <c r="G80">
-        <v>-16.62901442393121</v>
+        <v>-12.2481001508439</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-13.65236449006938</v>
       </c>
       <c r="E81">
-        <v>-29.91787435032585</v>
+        <v>-22.71926890642522</v>
       </c>
       <c r="F81">
-        <v>-3.022783211292142</v>
+        <v>-0.05499628748676973</v>
       </c>
       <c r="G81">
-        <v>-15.96783944011488</v>
+        <v>-11.86833602113138</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-13.538789275095</v>
       </c>
       <c r="E82">
-        <v>-30.89720781053741</v>
+        <v>-23.16424396776735</v>
       </c>
       <c r="F82">
-        <v>-2.810348390844208</v>
+        <v>0.05920078592836452</v>
       </c>
       <c r="G82">
-        <v>-15.99282687659643</v>
+        <v>-11.68427069522412</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-13.43747030367378</v>
       </c>
       <c r="E83">
-        <v>-31.15566007467583</v>
+        <v>-23.91480816517904</v>
       </c>
       <c r="F83">
-        <v>-2.86451285021106</v>
+        <v>-0.1071337318189706</v>
       </c>
       <c r="G83">
-        <v>-15.84610041983127</v>
+        <v>-11.74274615257588</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-13.3317179031743</v>
       </c>
       <c r="E84">
-        <v>-31.92865784305858</v>
+        <v>-24.62528972009481</v>
       </c>
       <c r="F84">
-        <v>-2.760440083192941</v>
+        <v>0.105576106606692</v>
       </c>
       <c r="G84">
-        <v>-16.3361476225616</v>
+        <v>-11.95145168593407</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-13.21982742095261</v>
       </c>
       <c r="E85">
-        <v>-31.58604282802817</v>
+        <v>-25.00544145907902</v>
       </c>
       <c r="F85">
-        <v>-2.545487025840497</v>
+        <v>-0.2733539348647194</v>
       </c>
       <c r="G85">
-        <v>-15.24749193014097</v>
+        <v>-12.08969191740581</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-13.09634724777551</v>
       </c>
       <c r="E86">
-        <v>-31.41902974102284</v>
+        <v>-25.78782340845022</v>
       </c>
       <c r="F86">
-        <v>-2.838480576210682</v>
+        <v>-0.2772754261495723</v>
       </c>
       <c r="G86">
-        <v>-16.04111259780907</v>
+        <v>-11.81055241109627</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-12.94706912790236</v>
       </c>
       <c r="E87">
-        <v>-34.26685352076717</v>
+        <v>-27.19943348637824</v>
       </c>
       <c r="F87">
-        <v>-2.49251624390108</v>
+        <v>-0.07125051266450162</v>
       </c>
       <c r="G87">
-        <v>-16.38154586025647</v>
+        <v>-11.48050469063232</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-12.78094490826747</v>
       </c>
       <c r="E88">
-        <v>-34.5678201326322</v>
+        <v>-27.67992265775898</v>
       </c>
       <c r="F88">
-        <v>-3.290589422412805</v>
+        <v>-0.05971301147831012</v>
       </c>
       <c r="G88">
-        <v>-15.69123757754791</v>
+        <v>-11.52632325820636</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-12.589095866833</v>
       </c>
       <c r="E89">
-        <v>-35.2952613259929</v>
+        <v>-30.04928818646041</v>
       </c>
       <c r="F89">
-        <v>-2.687786463395605</v>
+        <v>-0.1789366182936317</v>
       </c>
       <c r="G89">
-        <v>-14.77229855876178</v>
+        <v>-11.08930027812154</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-12.38479224291188</v>
       </c>
       <c r="E90">
-        <v>-36.87942279822791</v>
+        <v>-30.19928764327358</v>
       </c>
       <c r="F90">
-        <v>-2.647165811064526</v>
+        <v>-0.2160888963091896</v>
       </c>
       <c r="G90">
-        <v>-15.61654156405157</v>
+        <v>-11.38264092963444</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-12.17669542986616</v>
       </c>
       <c r="E91">
-        <v>-38.46231754100886</v>
+        <v>-31.82685225045872</v>
       </c>
       <c r="F91">
-        <v>-3.121186631805501</v>
+        <v>-0.502119190291442</v>
       </c>
       <c r="G91">
-        <v>-16.0106086580065</v>
+        <v>-11.31385955800927</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-11.96960069027536</v>
       </c>
       <c r="E92">
-        <v>-39.61341328537569</v>
+        <v>-33.80711586977094</v>
       </c>
       <c r="F92">
-        <v>-3.335636041777042</v>
+        <v>-0.2444729053661147</v>
       </c>
       <c r="G92">
-        <v>-15.34656968737372</v>
+        <v>-11.59747779666486</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-11.78430136980879</v>
       </c>
       <c r="E93">
-        <v>-38.06455410940172</v>
+        <v>-35.10298425449864</v>
       </c>
       <c r="F93">
-        <v>-2.811126227835437</v>
+        <v>-0.3195536416536535</v>
       </c>
       <c r="G93">
-        <v>-16.03346833764629</v>
+        <v>-11.69664823533059</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-11.61868771190207</v>
       </c>
       <c r="E94">
-        <v>-40.31318370828473</v>
+        <v>-36.53525863537335</v>
       </c>
       <c r="F94">
-        <v>-2.970229098156333</v>
+        <v>-0.4075908724883793</v>
       </c>
       <c r="G94">
-        <v>-15.96162456261574</v>
+        <v>-11.51436343723447</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-11.49031536115071</v>
       </c>
       <c r="E95">
-        <v>-41.34018772808266</v>
+        <v>-38.75562770779656</v>
       </c>
       <c r="F95">
-        <v>-3.138319754797603</v>
+        <v>-0.7521627191938757</v>
       </c>
       <c r="G95">
-        <v>-16.00291870981338</v>
+        <v>-11.42294560463205</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-11.40681071082046</v>
       </c>
       <c r="E96">
-        <v>-43.10955127632009</v>
+        <v>-40.19608391498118</v>
       </c>
       <c r="F96">
-        <v>-2.507504723687334</v>
+        <v>-1.001056474141224</v>
       </c>
       <c r="G96">
-        <v>-16.83883082911291</v>
+        <v>-11.59136343283247</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.36899927048742</v>
       </c>
       <c r="E97">
-        <v>-46.90712000049507</v>
+        <v>-42.03996645741434</v>
       </c>
       <c r="F97">
-        <v>-3.945609349032875</v>
+        <v>-0.7846247809747827</v>
       </c>
       <c r="G97">
-        <v>-16.20881769273612</v>
+        <v>-11.50775172655748</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.39325657097371</v>
       </c>
       <c r="E98">
-        <v>-46.17856782310498</v>
+        <v>-44.34054650015397</v>
       </c>
       <c r="F98">
-        <v>-2.684829191767611</v>
+        <v>-1.029565566675971</v>
       </c>
       <c r="G98">
-        <v>-16.75925794472037</v>
+        <v>-12.11522630487919</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.45736750237702</v>
       </c>
       <c r="E99">
-        <v>-49.72104111619483</v>
+        <v>-46.4136073967025</v>
       </c>
       <c r="F99">
-        <v>-3.420500625459046</v>
+        <v>-1.123716148943358</v>
       </c>
       <c r="G99">
-        <v>-16.87164919399551</v>
+        <v>-12.0359627937207</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.5752318986331</v>
       </c>
       <c r="E100">
-        <v>-49.17082679479004</v>
+        <v>-47.9129499106562</v>
       </c>
       <c r="F100">
-        <v>-3.042854553461974</v>
+        <v>-1.106081863672562</v>
       </c>
       <c r="G100">
-        <v>-16.42650027137085</v>
+        <v>-12.59445849814083</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.70896423646701</v>
       </c>
       <c r="E101">
-        <v>-50.48198834191859</v>
+        <v>-50.71494508003671</v>
       </c>
       <c r="F101">
-        <v>-2.918408918539404</v>
+        <v>-1.547466665478042</v>
       </c>
       <c r="G101">
-        <v>-16.57255054528691</v>
+        <v>-12.50752461937365</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.87860576121609</v>
       </c>
       <c r="E102">
-        <v>-53.42182236535317</v>
+        <v>-52.27257272342023</v>
       </c>
       <c r="F102">
-        <v>-4.034050823160167</v>
+        <v>-1.475381305719026</v>
       </c>
       <c r="G102">
-        <v>-17.14324625918131</v>
+        <v>-12.52881263076959</v>
       </c>
     </row>
   </sheetData>
